--- a/feedback_forms/023_point_of_sale_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/023_point_of_sale_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -823,12 +823,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>reason_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>Reason 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -869,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>product_rating</t>
+          <t>product_rating_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>product rating</t>
+          <t>Product Rating 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -892,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>product_name</t>
+          <t>product_name_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>product name</t>
+          <t>Product Name 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>employee_name_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>employee name</t>
+          <t>Employee Name 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -938,12 +938,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>customer_name_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>customer name</t>
+          <t>Customer Name 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>store_name</t>
+          <t>store_name_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>store name</t>
+          <t>Store Name 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>store_rating</t>
+          <t>store_rating_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>store rating</t>
+          <t>Store Rating 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>product_rating</t>
+          <t>product_rating_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>product rating</t>
+          <t>Product Rating 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1323,29 +1323,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>customer_choices</t>
+          <t>employee_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option 3</t>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>customer_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
